--- a/data-raw/workbooks/kelpbio-2-prefit-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-2-prefit-nereo.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="size" sheetId="1" r:id="rId1"/>
+    <sheet name="size_sample" sheetId="1" r:id="rId1"/>
     <sheet name="survey" sheetId="2" r:id="rId2"/>
     <sheet name="canopy" sheetId="3" r:id="rId3"/>
   </sheets>
